--- a/Resource/素材/素材リスト.xlsx
+++ b/Resource/素材/素材リスト.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\K245018\Documents\発注書（ドーナツ）\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\K245018\Documents\就職活動用作品\Team\Resource\素材\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D43E9618-5912-40FC-81D8-37060BA66767}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F22B485-7521-4413-98C7-62B4E36D1D34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{70EB8D72-4295-4E6B-9ACE-1CC86D0A1DFE}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="43">
   <si>
     <t>イメージ</t>
     <phoneticPr fontId="1"/>
@@ -198,6 +198,173 @@
       <t>マエ</t>
     </rPh>
     <rPh sb="8" eb="9">
+      <t>オト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボスの形態変化の合図</t>
+    <rPh sb="3" eb="7">
+      <t>ケイタイヘンカ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>アイズ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「がおーん」とか</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>剣を振る音とか？</t>
+    <rPh sb="0" eb="1">
+      <t>ケン</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>オト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>早め</t>
+    <rPh sb="0" eb="1">
+      <t>ハヤ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>空に浮かぶ雑魚敵に風を切る音</t>
+    <rPh sb="0" eb="1">
+      <t>ソラ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>ザコテキ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>カゼ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>オト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「ふーーん」とか</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボスキャラが岩を投げた時の音</t>
+    <rPh sb="6" eb="7">
+      <t>イワ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ナ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>オト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「ぶおーーん」とか</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボスキャラが岩を出した時の音</t>
+    <rPh sb="8" eb="9">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>オト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「ゴゴゴゴゴゴ」とか</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージ０</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>〇</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>雑魚敵が空から降ってくる音</t>
+    <rPh sb="0" eb="3">
+      <t>ザコテキ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ソラ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>オト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージ１の方のボスが岩を振った時の音</t>
+    <rPh sb="6" eb="7">
+      <t>ホウ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>イワ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>オト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「ブーーン」とか</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージ１の方のボスのビームを貯める音</t>
+    <rPh sb="15" eb="16">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>オト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージ１の方のボスのビームを撃った時の音</t>
+    <rPh sb="15" eb="16">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
       <t>オト</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -248,7 +415,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -333,13 +500,61 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -358,41 +573,53 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -711,517 +938,560 @@
   <dimension ref="A1:P26"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
+    <col min="1" max="1" width="5" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="8.6640625" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="15.33203125" customWidth="1"/>
     <col min="13" max="14" width="8.6640625" customWidth="1"/>
     <col min="15" max="15" width="76.9140625" customWidth="1"/>
     <col min="16" max="16" width="51.08203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="7"/>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="16"/>
+      <c r="N1" s="16"/>
+      <c r="O1" s="16"/>
       <c r="P1" s="3"/>
     </row>
     <row r="2" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="7"/>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
+      <c r="A2" s="16"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="16"/>
+      <c r="N2" s="16"/>
+      <c r="O2" s="16"/>
       <c r="P2" s="3"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6" t="s">
+      <c r="B3" s="9"/>
+      <c r="C3" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6" t="s">
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6" t="s">
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="12"/>
-      <c r="O3" s="13"/>
-      <c r="P3" s="10"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+      <c r="N3" s="20"/>
+      <c r="O3" s="21"/>
+      <c r="P3" s="6"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
+      <c r="A4" s="9"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
       <c r="N4" s="14"/>
       <c r="O4" s="15"/>
-      <c r="P4" s="10"/>
+      <c r="P4" s="6"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6" t="s">
+      <c r="B5" s="9"/>
+      <c r="C5" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6" t="s">
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6" t="s">
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="L5" s="6"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="16" t="s">
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
+      <c r="N5" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="O5" s="17"/>
+      <c r="O5" s="18"/>
       <c r="P5" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="6"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6" t="s">
+      <c r="A6" s="9"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6" t="s">
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6" t="s">
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="L6" s="6"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="11" t="s">
+      <c r="L6" s="9"/>
+      <c r="M6" s="9"/>
+      <c r="N6" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="O6" s="8"/>
+      <c r="O6" s="7"/>
       <c r="P6" s="4"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6" t="s">
+      <c r="A7" s="9"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6" t="s">
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="11"/>
-      <c r="O7" s="8"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="7"/>
       <c r="P7" s="4"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6" t="s">
+      <c r="A8" s="19"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6" t="s">
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="11"/>
-      <c r="O8" s="8"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="9"/>
+      <c r="M8" s="9"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="7"/>
       <c r="P8" s="4"/>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6" t="s">
+      <c r="A9" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="21"/>
+      <c r="C9" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6" t="s">
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="6"/>
-      <c r="M9" s="6"/>
-      <c r="N9" s="11"/>
-      <c r="O9" s="8"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
+      <c r="K9" s="9"/>
+      <c r="L9" s="9"/>
+      <c r="M9" s="9"/>
+      <c r="N9" s="8"/>
+      <c r="O9" s="7"/>
       <c r="P9" s="4"/>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6" t="s">
+      <c r="B10" s="13"/>
+      <c r="C10" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6" t="s">
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
-      <c r="J10" s="6"/>
-      <c r="K10" s="6"/>
-      <c r="L10" s="6"/>
-      <c r="M10" s="6"/>
-      <c r="N10" s="11"/>
-      <c r="O10" s="8"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="9"/>
+      <c r="K10" s="9"/>
+      <c r="L10" s="9"/>
+      <c r="M10" s="9"/>
+      <c r="N10" s="8"/>
+      <c r="O10" s="7"/>
       <c r="P10" s="4"/>
     </row>
-    <row r="11" spans="1:16" ht="18.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:16" ht="19" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="6"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6" t="s">
+      <c r="B11" s="13"/>
+      <c r="C11" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6" t="s">
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
-      <c r="L11" s="6"/>
-      <c r="M11" s="6"/>
-      <c r="N11" s="11"/>
-      <c r="O11" s="8"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="L11" s="9"/>
+      <c r="M11" s="9"/>
+      <c r="N11" s="8"/>
+      <c r="O11" s="7"/>
       <c r="P11" s="4"/>
     </row>
-    <row r="12" spans="1:16" ht="17" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6" t="s">
+      <c r="B12" s="13"/>
+      <c r="C12" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6" t="s">
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6"/>
-      <c r="M12" s="6"/>
-      <c r="N12" s="11"/>
-      <c r="O12" s="8"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="L12" s="9"/>
+      <c r="M12" s="9"/>
+      <c r="N12" s="8"/>
+      <c r="O12" s="7"/>
       <c r="P12" s="4"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:16" ht="23" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6" t="s">
+      <c r="B13" s="13"/>
+      <c r="C13" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="6"/>
-      <c r="L13" s="6"/>
-      <c r="M13" s="6"/>
-      <c r="N13" s="11"/>
-      <c r="O13" s="8"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="L13" s="9"/>
+      <c r="M13" s="9"/>
+      <c r="N13" s="8"/>
+      <c r="O13" s="7"/>
       <c r="P13" s="5"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:16" ht="17" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="6"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
-      <c r="L14" s="6"/>
-      <c r="M14" s="6"/>
-      <c r="N14" s="11"/>
-      <c r="O14" s="8"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="H14" s="9"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="9"/>
+      <c r="K14" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="L14" s="9"/>
+      <c r="M14" s="9"/>
+      <c r="N14" s="8"/>
+      <c r="O14" s="7"/>
       <c r="P14" s="4"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:16" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="6"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-      <c r="K15" s="6"/>
-      <c r="L15" s="6"/>
-      <c r="M15" s="6"/>
-      <c r="N15" s="11"/>
-      <c r="O15" s="8"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="H15" s="9"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="9"/>
+      <c r="K15" s="9"/>
+      <c r="L15" s="9"/>
+      <c r="M15" s="9"/>
+      <c r="N15" s="8"/>
+      <c r="O15" s="7"/>
       <c r="P15" s="4"/>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
-      <c r="K16" s="6"/>
-      <c r="L16" s="6"/>
-      <c r="M16" s="6"/>
-      <c r="N16" s="11"/>
-      <c r="O16" s="8"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H16" s="9"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="9"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="8"/>
+      <c r="O16" s="7"/>
       <c r="P16" s="4"/>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
-      <c r="K17" s="6"/>
-      <c r="L17" s="6"/>
-      <c r="M17" s="6"/>
-      <c r="N17" s="8"/>
-      <c r="O17" s="8"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="9"/>
+      <c r="K17" s="9"/>
+      <c r="L17" s="9"/>
+      <c r="M17" s="9"/>
+      <c r="N17" s="7"/>
+      <c r="O17" s="7"/>
       <c r="P17" s="5"/>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="6"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-      <c r="K18" s="6"/>
-      <c r="L18" s="6"/>
-      <c r="M18" s="6"/>
-      <c r="N18" s="8"/>
-      <c r="O18" s="8"/>
+      <c r="A18" s="14"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H18" s="9"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="9"/>
+      <c r="K18" s="9"/>
+      <c r="L18" s="9"/>
+      <c r="M18" s="9"/>
+      <c r="N18" s="7"/>
+      <c r="O18" s="7"/>
       <c r="P18" s="4"/>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="6"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
-      <c r="K19" s="6"/>
-      <c r="L19" s="6"/>
-      <c r="M19" s="6"/>
-      <c r="N19" s="8"/>
-      <c r="O19" s="8"/>
+      <c r="A19" s="10"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="H19" s="9"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="9"/>
+      <c r="K19" s="9"/>
+      <c r="L19" s="9"/>
+      <c r="M19" s="9"/>
+      <c r="N19" s="7"/>
+      <c r="O19" s="7"/>
       <c r="P19" s="4"/>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="6"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
-      <c r="J20" s="6"/>
-      <c r="K20" s="6"/>
-      <c r="L20" s="6"/>
-      <c r="M20" s="6"/>
-      <c r="N20" s="8"/>
-      <c r="O20" s="8"/>
+      <c r="A20" s="9"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="9"/>
+      <c r="K20" s="9"/>
+      <c r="L20" s="9"/>
+      <c r="M20" s="9"/>
+      <c r="N20" s="7"/>
+      <c r="O20" s="7"/>
       <c r="P20" s="4"/>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="6"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="6"/>
-      <c r="K21" s="6"/>
-      <c r="L21" s="6"/>
-      <c r="M21" s="6"/>
-      <c r="N21" s="8"/>
-      <c r="O21" s="8"/>
+      <c r="A21" s="9"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="9"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="9"/>
+      <c r="K21" s="9"/>
+      <c r="L21" s="9"/>
+      <c r="M21" s="9"/>
+      <c r="N21" s="7"/>
+      <c r="O21" s="7"/>
       <c r="P21" s="4"/>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="6"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="6"/>
-      <c r="K22" s="6"/>
-      <c r="L22" s="6"/>
-      <c r="M22" s="6"/>
-      <c r="N22" s="8"/>
-      <c r="O22" s="8"/>
+      <c r="A22" s="9"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="9"/>
+      <c r="I22" s="9"/>
+      <c r="J22" s="9"/>
+      <c r="K22" s="9"/>
+      <c r="L22" s="9"/>
+      <c r="M22" s="9"/>
+      <c r="N22" s="7"/>
+      <c r="O22" s="7"/>
       <c r="P22" s="4"/>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="6"/>
-      <c r="B23" s="6"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
-      <c r="J23" s="6"/>
-      <c r="K23" s="6"/>
-      <c r="L23" s="6"/>
-      <c r="M23" s="6"/>
-      <c r="N23" s="8"/>
-      <c r="O23" s="8"/>
+      <c r="A23" s="9"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="9"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="9"/>
+      <c r="K23" s="9"/>
+      <c r="L23" s="9"/>
+      <c r="M23" s="9"/>
+      <c r="N23" s="7"/>
+      <c r="O23" s="7"/>
       <c r="P23" s="4"/>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="6"/>
-      <c r="B24" s="6"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6"/>
-      <c r="J24" s="6"/>
-      <c r="K24" s="6"/>
-      <c r="L24" s="6"/>
-      <c r="M24" s="6"/>
-      <c r="N24" s="8"/>
-      <c r="O24" s="8"/>
+      <c r="A24" s="9"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="9"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="9"/>
+      <c r="I24" s="9"/>
+      <c r="J24" s="9"/>
+      <c r="K24" s="9"/>
+      <c r="L24" s="9"/>
+      <c r="M24" s="9"/>
+      <c r="N24" s="7"/>
+      <c r="O24" s="7"/>
       <c r="P24" s="4"/>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="6"/>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="6"/>
-      <c r="I25" s="6"/>
-      <c r="J25" s="6"/>
-      <c r="K25" s="6"/>
-      <c r="L25" s="6"/>
-      <c r="M25" s="6"/>
-      <c r="N25" s="8"/>
-      <c r="O25" s="8"/>
+      <c r="A25" s="9"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="9"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="9"/>
+      <c r="K25" s="9"/>
+      <c r="L25" s="9"/>
+      <c r="M25" s="9"/>
+      <c r="N25" s="7"/>
+      <c r="O25" s="7"/>
       <c r="P25" s="4"/>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.55000000000000004">
@@ -1230,60 +1500,25 @@
     </row>
   </sheetData>
   <mergeCells count="97">
-    <mergeCell ref="N24:O24"/>
-    <mergeCell ref="N23:O23"/>
-    <mergeCell ref="N25:O25"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="N21:O21"/>
-    <mergeCell ref="N22:O22"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="G23:J23"/>
-    <mergeCell ref="N11:O11"/>
-    <mergeCell ref="N12:O12"/>
-    <mergeCell ref="N13:O13"/>
-    <mergeCell ref="N14:O14"/>
-    <mergeCell ref="N15:O15"/>
-    <mergeCell ref="N16:O16"/>
-    <mergeCell ref="N17:O17"/>
-    <mergeCell ref="N18:O18"/>
-    <mergeCell ref="N19:O19"/>
-    <mergeCell ref="N20:O20"/>
-    <mergeCell ref="A22:B25"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="G25:J25"/>
-    <mergeCell ref="K25:M25"/>
-    <mergeCell ref="K22:M22"/>
-    <mergeCell ref="K23:M23"/>
-    <mergeCell ref="K24:M24"/>
-    <mergeCell ref="G22:J22"/>
-    <mergeCell ref="G24:J24"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="A17:B18"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="G21:J21"/>
-    <mergeCell ref="K21:M21"/>
-    <mergeCell ref="K17:M17"/>
-    <mergeCell ref="G18:J18"/>
-    <mergeCell ref="K18:M18"/>
-    <mergeCell ref="G17:J17"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="G19:J19"/>
-    <mergeCell ref="K19:M19"/>
-    <mergeCell ref="A19:B21"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="G20:J20"/>
-    <mergeCell ref="K20:M20"/>
-    <mergeCell ref="G3:J4"/>
-    <mergeCell ref="K3:M4"/>
-    <mergeCell ref="G6:J6"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="C7:F7"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="G8:J8"/>
+    <mergeCell ref="G10:J10"/>
+    <mergeCell ref="K10:M10"/>
+    <mergeCell ref="K9:M9"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="A9:B15"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="G14:J14"/>
+    <mergeCell ref="K14:M14"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="G15:J15"/>
+    <mergeCell ref="K15:M15"/>
+    <mergeCell ref="G11:J11"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="G12:J12"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="G13:J13"/>
+    <mergeCell ref="K13:M13"/>
+    <mergeCell ref="G9:J9"/>
     <mergeCell ref="A1:O2"/>
     <mergeCell ref="C3:F4"/>
     <mergeCell ref="C5:F5"/>
@@ -1297,27 +1532,18 @@
     <mergeCell ref="N8:O8"/>
     <mergeCell ref="N7:O7"/>
     <mergeCell ref="K8:M8"/>
-    <mergeCell ref="K9:M9"/>
+    <mergeCell ref="G3:J4"/>
     <mergeCell ref="G7:J7"/>
     <mergeCell ref="K7:M7"/>
-    <mergeCell ref="N10:O10"/>
-    <mergeCell ref="A9:B15"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="G14:J14"/>
-    <mergeCell ref="K14:M14"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="G15:J15"/>
-    <mergeCell ref="K15:M15"/>
-    <mergeCell ref="G11:J11"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="G12:J12"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="K3:M4"/>
+    <mergeCell ref="G6:J6"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="A17:B18"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="G8:J8"/>
+    <mergeCell ref="C7:F7"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="G13:J13"/>
-    <mergeCell ref="K13:M13"/>
-    <mergeCell ref="G9:J9"/>
     <mergeCell ref="C16:F16"/>
     <mergeCell ref="G16:J16"/>
     <mergeCell ref="K16:M16"/>
@@ -1325,8 +1551,52 @@
     <mergeCell ref="C10:F10"/>
     <mergeCell ref="C11:F11"/>
     <mergeCell ref="C12:F12"/>
-    <mergeCell ref="G10:J10"/>
-    <mergeCell ref="K10:M10"/>
+    <mergeCell ref="G18:J18"/>
+    <mergeCell ref="K18:M18"/>
+    <mergeCell ref="G17:J17"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="G22:J22"/>
+    <mergeCell ref="G24:J24"/>
+    <mergeCell ref="G23:J23"/>
+    <mergeCell ref="N25:O25"/>
+    <mergeCell ref="A19:B21"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="G20:J20"/>
+    <mergeCell ref="A22:B25"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="G25:J25"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="G21:J21"/>
+    <mergeCell ref="G19:J19"/>
+    <mergeCell ref="K17:M17"/>
+    <mergeCell ref="K19:M19"/>
+    <mergeCell ref="K20:M20"/>
+    <mergeCell ref="N24:O24"/>
+    <mergeCell ref="N23:O23"/>
+    <mergeCell ref="K25:M25"/>
+    <mergeCell ref="K22:M22"/>
+    <mergeCell ref="K23:M23"/>
+    <mergeCell ref="K24:M24"/>
+    <mergeCell ref="K21:M21"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="N21:O21"/>
+    <mergeCell ref="N22:O22"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="N16:O16"/>
+    <mergeCell ref="N17:O17"/>
+    <mergeCell ref="N18:O18"/>
+    <mergeCell ref="N19:O19"/>
+    <mergeCell ref="N20:O20"/>
+    <mergeCell ref="N11:O11"/>
+    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="N14:O14"/>
+    <mergeCell ref="N15:O15"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Resource/素材/素材リスト.xlsx
+++ b/Resource/素材/素材リスト.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\K245018\Documents\就職活動用作品\Team\Resource\素材\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k245020\Documents\就職作品\Team\Resource\素材\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F22B485-7521-4413-98C7-62B4E36D1D34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19465F38-84DC-4DC3-BD16-D563AE476EC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{70EB8D72-4295-4E6B-9ACE-1CC86D0A1DFE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{70EB8D72-4295-4E6B-9ACE-1CC86D0A1DFE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -573,52 +573,52 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -936,570 +936,651 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EF7177C-6477-4959-A104-F00A3D372571}">
   <dimension ref="A1:P26"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="8.6640625" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="15.33203125" customWidth="1"/>
-    <col min="13" max="14" width="8.6640625" customWidth="1"/>
-    <col min="15" max="15" width="76.9140625" customWidth="1"/>
-    <col min="16" max="16" width="51.08203125" customWidth="1"/>
+    <col min="2" max="2" width="8.69921875" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="15.296875" customWidth="1"/>
+    <col min="13" max="14" width="8.69921875" customWidth="1"/>
+    <col min="15" max="15" width="76.8984375" customWidth="1"/>
+    <col min="16" max="16" width="51.09765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
-      <c r="N1" s="16"/>
-      <c r="O1" s="16"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
+      <c r="O1" s="14"/>
       <c r="P1" s="3"/>
     </row>
-    <row r="2" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="16"/>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-      <c r="M2" s="16"/>
-      <c r="N2" s="16"/>
-      <c r="O2" s="16"/>
+    <row r="2" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="14"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="14"/>
       <c r="P2" s="3"/>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="9" t="s">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9" t="s">
+      <c r="B3" s="6"/>
+      <c r="C3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9" t="s">
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9" t="s">
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
-      <c r="N3" s="20"/>
-      <c r="O3" s="21"/>
-      <c r="P3" s="6"/>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="9"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
-      <c r="N4" s="14"/>
-      <c r="O4" s="15"/>
-      <c r="P4" s="6"/>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="9" t="s">
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="9"/>
+      <c r="O3" s="10"/>
+      <c r="P3" s="11"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="18"/>
+      <c r="O4" s="19"/>
+      <c r="P4" s="11"/>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A5" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9" t="s">
+      <c r="B5" s="6"/>
+      <c r="C5" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9" t="s">
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9" t="s">
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="L5" s="9"/>
-      <c r="M5" s="9"/>
-      <c r="N5" s="17" t="s">
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="O5" s="18"/>
+      <c r="O5" s="16"/>
       <c r="P5" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="9"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9" t="s">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A6" s="6"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9" t="s">
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
-      <c r="K6" s="9" t="s">
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="L6" s="9"/>
-      <c r="M6" s="9"/>
-      <c r="N6" s="8" t="s">
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="O6" s="7"/>
+      <c r="O6" s="8"/>
       <c r="P6" s="4"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="9"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9" t="s">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A7" s="6"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9" t="s">
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9" t="s">
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="L7" s="9"/>
-      <c r="M7" s="9"/>
-      <c r="N7" s="8"/>
-      <c r="O7" s="7"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="7"/>
+      <c r="O7" s="8"/>
       <c r="P7" s="4"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="19"/>
-      <c r="B8" s="19"/>
-      <c r="C8" s="9" t="s">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A8" s="17"/>
+      <c r="B8" s="17"/>
+      <c r="C8" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9" t="s">
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
-      <c r="K8" s="9"/>
-      <c r="L8" s="9"/>
-      <c r="M8" s="9"/>
-      <c r="N8" s="8"/>
-      <c r="O8" s="7"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="7"/>
+      <c r="O8" s="8"/>
       <c r="P8" s="4"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="20" t="s">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A9" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="B9" s="21"/>
-      <c r="C9" s="12" t="s">
+      <c r="B9" s="10"/>
+      <c r="C9" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9" t="s">
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9"/>
-      <c r="L9" s="9"/>
-      <c r="M9" s="9"/>
-      <c r="N9" s="8"/>
-      <c r="O9" s="7"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="7"/>
+      <c r="O9" s="8"/>
       <c r="P9" s="4"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="6"/>
-      <c r="B10" s="13"/>
-      <c r="C10" s="12" t="s">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A10" s="11"/>
+      <c r="B10" s="12"/>
+      <c r="C10" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9" t="s">
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
-      <c r="K10" s="9"/>
-      <c r="L10" s="9"/>
-      <c r="M10" s="9"/>
-      <c r="N10" s="8"/>
-      <c r="O10" s="7"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="7"/>
+      <c r="O10" s="8"/>
       <c r="P10" s="4"/>
     </row>
-    <row r="11" spans="1:16" ht="19" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="6"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="12" t="s">
+    <row r="11" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A11" s="11"/>
+      <c r="B11" s="12"/>
+      <c r="C11" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9" t="s">
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
-      <c r="K11" s="9" t="s">
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="L11" s="9"/>
-      <c r="M11" s="9"/>
-      <c r="N11" s="8"/>
-      <c r="O11" s="7"/>
+      <c r="L11" s="6"/>
+      <c r="M11" s="6"/>
+      <c r="N11" s="7"/>
+      <c r="O11" s="8"/>
       <c r="P11" s="4"/>
     </row>
-    <row r="12" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="6"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="12" t="s">
+    <row r="12" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="11"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9" t="s">
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
-      <c r="K12" s="9" t="s">
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
+      <c r="K12" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="L12" s="9"/>
-      <c r="M12" s="9"/>
-      <c r="N12" s="8"/>
-      <c r="O12" s="7"/>
+      <c r="L12" s="6"/>
+      <c r="M12" s="6"/>
+      <c r="N12" s="7"/>
+      <c r="O12" s="8"/>
       <c r="P12" s="4"/>
     </row>
-    <row r="13" spans="1:16" ht="23" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="6"/>
-      <c r="B13" s="13"/>
-      <c r="C13" s="12" t="s">
+    <row r="13" spans="1:16" ht="22.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="11"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9" t="s">
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="9"/>
-      <c r="K13" s="9" t="s">
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="L13" s="9"/>
-      <c r="M13" s="9"/>
-      <c r="N13" s="8"/>
-      <c r="O13" s="7"/>
+      <c r="L13" s="6"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="7"/>
+      <c r="O13" s="8"/>
       <c r="P13" s="5"/>
     </row>
-    <row r="14" spans="1:16" ht="17" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="6"/>
-      <c r="B14" s="13"/>
-      <c r="C14" s="12" t="s">
+    <row r="14" spans="1:16" ht="16.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="11"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9" t="s">
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
-      <c r="K14" s="9" t="s">
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
+      <c r="K14" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="L14" s="9"/>
-      <c r="M14" s="9"/>
-      <c r="N14" s="8"/>
-      <c r="O14" s="7"/>
+      <c r="L14" s="6"/>
+      <c r="M14" s="6"/>
+      <c r="N14" s="7"/>
+      <c r="O14" s="8"/>
       <c r="P14" s="4"/>
     </row>
-    <row r="15" spans="1:16" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="6"/>
-      <c r="B15" s="13"/>
-      <c r="C15" s="12" t="s">
+    <row r="15" spans="1:16" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A15" s="11"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9" t="s">
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
-      <c r="K15" s="9"/>
-      <c r="L15" s="9"/>
-      <c r="M15" s="9"/>
-      <c r="N15" s="8"/>
-      <c r="O15" s="7"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6"/>
+      <c r="M15" s="6"/>
+      <c r="N15" s="7"/>
+      <c r="O15" s="8"/>
       <c r="P15" s="4"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="6"/>
-      <c r="B16" s="13"/>
-      <c r="C16" s="12" t="s">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A16" s="11"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9" t="s">
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="9"/>
-      <c r="K16" s="9"/>
-      <c r="L16" s="9"/>
-      <c r="M16" s="9"/>
-      <c r="N16" s="8"/>
-      <c r="O16" s="7"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="6"/>
+      <c r="M16" s="6"/>
+      <c r="N16" s="7"/>
+      <c r="O16" s="8"/>
       <c r="P16" s="4"/>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="6"/>
-      <c r="B17" s="13"/>
-      <c r="C17" s="12" t="s">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A17" s="11"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9" t="s">
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
-      <c r="K17" s="9"/>
-      <c r="L17" s="9"/>
-      <c r="M17" s="9"/>
-      <c r="N17" s="7"/>
-      <c r="O17" s="7"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="8"/>
+      <c r="O17" s="8"/>
       <c r="P17" s="5"/>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="14"/>
-      <c r="B18" s="15"/>
-      <c r="C18" s="12" t="s">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A18" s="18"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9" t="s">
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9"/>
-      <c r="K18" s="9"/>
-      <c r="L18" s="9"/>
-      <c r="M18" s="9"/>
-      <c r="N18" s="7"/>
-      <c r="O18" s="7"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="6"/>
+      <c r="L18" s="6"/>
+      <c r="M18" s="6"/>
+      <c r="N18" s="8"/>
+      <c r="O18" s="8"/>
       <c r="P18" s="4"/>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="10"/>
-      <c r="B19" s="10"/>
-      <c r="C19" s="9" t="s">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A19" s="20"/>
+      <c r="B19" s="20"/>
+      <c r="C19" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9" t="s">
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="9"/>
-      <c r="K19" s="9"/>
-      <c r="L19" s="9"/>
-      <c r="M19" s="9"/>
-      <c r="N19" s="7"/>
-      <c r="O19" s="7"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="6"/>
+      <c r="K19" s="6"/>
+      <c r="L19" s="6"/>
+      <c r="M19" s="6"/>
+      <c r="N19" s="8"/>
+      <c r="O19" s="8"/>
       <c r="P19" s="4"/>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9" t="s">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A20" s="6"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9"/>
-      <c r="K20" s="9"/>
-      <c r="L20" s="9"/>
-      <c r="M20" s="9"/>
-      <c r="N20" s="7"/>
-      <c r="O20" s="7"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="6"/>
+      <c r="J20" s="6"/>
+      <c r="K20" s="6"/>
+      <c r="L20" s="6"/>
+      <c r="M20" s="6"/>
+      <c r="N20" s="8"/>
+      <c r="O20" s="8"/>
       <c r="P20" s="4"/>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="9"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9" t="s">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A21" s="6"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="9"/>
-      <c r="K21" s="9"/>
-      <c r="L21" s="9"/>
-      <c r="M21" s="9"/>
-      <c r="N21" s="7"/>
-      <c r="O21" s="7"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="6"/>
+      <c r="J21" s="6"/>
+      <c r="K21" s="6"/>
+      <c r="L21" s="6"/>
+      <c r="M21" s="6"/>
+      <c r="N21" s="8"/>
+      <c r="O21" s="8"/>
       <c r="P21" s="4"/>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="9"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="9"/>
-      <c r="J22" s="9"/>
-      <c r="K22" s="9"/>
-      <c r="L22" s="9"/>
-      <c r="M22" s="9"/>
-      <c r="N22" s="7"/>
-      <c r="O22" s="7"/>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A22" s="6"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
+      <c r="J22" s="6"/>
+      <c r="K22" s="6"/>
+      <c r="L22" s="6"/>
+      <c r="M22" s="6"/>
+      <c r="N22" s="8"/>
+      <c r="O22" s="8"/>
       <c r="P22" s="4"/>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="9"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="9"/>
-      <c r="J23" s="9"/>
-      <c r="K23" s="9"/>
-      <c r="L23" s="9"/>
-      <c r="M23" s="9"/>
-      <c r="N23" s="7"/>
-      <c r="O23" s="7"/>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A23" s="6"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="6"/>
+      <c r="J23" s="6"/>
+      <c r="K23" s="6"/>
+      <c r="L23" s="6"/>
+      <c r="M23" s="6"/>
+      <c r="N23" s="8"/>
+      <c r="O23" s="8"/>
       <c r="P23" s="4"/>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="9"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="11"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="9"/>
-      <c r="K24" s="9"/>
-      <c r="L24" s="9"/>
-      <c r="M24" s="9"/>
-      <c r="N24" s="7"/>
-      <c r="O24" s="7"/>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A24" s="6"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="6"/>
+      <c r="J24" s="6"/>
+      <c r="K24" s="6"/>
+      <c r="L24" s="6"/>
+      <c r="M24" s="6"/>
+      <c r="N24" s="8"/>
+      <c r="O24" s="8"/>
       <c r="P24" s="4"/>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="9"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
-      <c r="J25" s="9"/>
-      <c r="K25" s="9"/>
-      <c r="L25" s="9"/>
-      <c r="M25" s="9"/>
-      <c r="N25" s="7"/>
-      <c r="O25" s="7"/>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A25" s="6"/>
+      <c r="B25" s="6"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="6"/>
+      <c r="J25" s="6"/>
+      <c r="K25" s="6"/>
+      <c r="L25" s="6"/>
+      <c r="M25" s="6"/>
+      <c r="N25" s="8"/>
+      <c r="O25" s="8"/>
       <c r="P25" s="4"/>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="97">
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="N21:O21"/>
+    <mergeCell ref="N22:O22"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="N16:O16"/>
+    <mergeCell ref="N17:O17"/>
+    <mergeCell ref="N18:O18"/>
+    <mergeCell ref="N19:O19"/>
+    <mergeCell ref="N20:O20"/>
+    <mergeCell ref="N11:O11"/>
+    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="N14:O14"/>
+    <mergeCell ref="N15:O15"/>
+    <mergeCell ref="K17:M17"/>
+    <mergeCell ref="K19:M19"/>
+    <mergeCell ref="K20:M20"/>
+    <mergeCell ref="N24:O24"/>
+    <mergeCell ref="N23:O23"/>
+    <mergeCell ref="K22:M22"/>
+    <mergeCell ref="K23:M23"/>
+    <mergeCell ref="K24:M24"/>
+    <mergeCell ref="K21:M21"/>
+    <mergeCell ref="N25:O25"/>
+    <mergeCell ref="A19:B21"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="G20:J20"/>
+    <mergeCell ref="A22:B25"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="G25:J25"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="G21:J21"/>
+    <mergeCell ref="G19:J19"/>
+    <mergeCell ref="K25:M25"/>
+    <mergeCell ref="G17:J17"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="G22:J22"/>
+    <mergeCell ref="G24:J24"/>
+    <mergeCell ref="G23:J23"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="A17:B18"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="G8:J8"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="G16:J16"/>
+    <mergeCell ref="K16:M16"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="G18:J18"/>
+    <mergeCell ref="K18:M18"/>
+    <mergeCell ref="G3:J4"/>
+    <mergeCell ref="G7:J7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="K3:M4"/>
+    <mergeCell ref="G6:J6"/>
+    <mergeCell ref="G13:J13"/>
+    <mergeCell ref="K13:M13"/>
+    <mergeCell ref="G9:J9"/>
+    <mergeCell ref="A1:O2"/>
+    <mergeCell ref="C3:F4"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="G5:J5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="A5:B8"/>
+    <mergeCell ref="N3:O4"/>
+    <mergeCell ref="A3:B4"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="K8:M8"/>
     <mergeCell ref="G10:J10"/>
     <mergeCell ref="K10:M10"/>
     <mergeCell ref="K9:M9"/>
@@ -1516,87 +1597,6 @@
     <mergeCell ref="G12:J12"/>
     <mergeCell ref="K12:M12"/>
     <mergeCell ref="C13:F13"/>
-    <mergeCell ref="G13:J13"/>
-    <mergeCell ref="K13:M13"/>
-    <mergeCell ref="G9:J9"/>
-    <mergeCell ref="A1:O2"/>
-    <mergeCell ref="C3:F4"/>
-    <mergeCell ref="C5:F5"/>
-    <mergeCell ref="G5:J5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="N5:O5"/>
-    <mergeCell ref="A5:B8"/>
-    <mergeCell ref="N3:O4"/>
-    <mergeCell ref="A3:B4"/>
-    <mergeCell ref="N6:O6"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="G3:J4"/>
-    <mergeCell ref="G7:J7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="K3:M4"/>
-    <mergeCell ref="G6:J6"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="A17:B18"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="G8:J8"/>
-    <mergeCell ref="C7:F7"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="G16:J16"/>
-    <mergeCell ref="K16:M16"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="G18:J18"/>
-    <mergeCell ref="K18:M18"/>
-    <mergeCell ref="G17:J17"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="G22:J22"/>
-    <mergeCell ref="G24:J24"/>
-    <mergeCell ref="G23:J23"/>
-    <mergeCell ref="N25:O25"/>
-    <mergeCell ref="A19:B21"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="G20:J20"/>
-    <mergeCell ref="A22:B25"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="G25:J25"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="G21:J21"/>
-    <mergeCell ref="G19:J19"/>
-    <mergeCell ref="K17:M17"/>
-    <mergeCell ref="K19:M19"/>
-    <mergeCell ref="K20:M20"/>
-    <mergeCell ref="N24:O24"/>
-    <mergeCell ref="N23:O23"/>
-    <mergeCell ref="K25:M25"/>
-    <mergeCell ref="K22:M22"/>
-    <mergeCell ref="K23:M23"/>
-    <mergeCell ref="K24:M24"/>
-    <mergeCell ref="K21:M21"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="N21:O21"/>
-    <mergeCell ref="N22:O22"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="N16:O16"/>
-    <mergeCell ref="N17:O17"/>
-    <mergeCell ref="N18:O18"/>
-    <mergeCell ref="N19:O19"/>
-    <mergeCell ref="N20:O20"/>
-    <mergeCell ref="N11:O11"/>
-    <mergeCell ref="N12:O12"/>
-    <mergeCell ref="N13:O13"/>
-    <mergeCell ref="N14:O14"/>
-    <mergeCell ref="N15:O15"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
